--- a/yas/main/output/metrics_yas_main.xlsx
+++ b/yas/main/output/metrics_yas_main.xlsx
@@ -1165,17 +1165,17 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>True Positive Rate (TPR)</t>
+          <t>True Negative Rate</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>False Positive Rate (FPR)</t>
+          <t>False Negative Rate</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>False Negative Rate (FNR)</t>
+          <t>False Positive Rate</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -1247,47 +1247,47 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>True Positives: correctly flags inconsistency (TP)</t>
+          <t>Cases that correctly captures inconsistency (TN)</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>False Negatives: misses real inconsistency (FN)</t>
+          <t>Cases that missed inconsistency (FP)</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>TPR = TP/(TP+FN)</t>
+          <t>TNR</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>False Positives: false alarm (FP)</t>
+          <t>Cases that incorrectly captures inconsistencies (FN)</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>True Negatives: correctly reports consistent (TN)</t>
+          <t>Cases that tests consistency (TP)</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>FPR = FP/(FP+TN)</t>
+          <t>FNR</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t>False Positives: false alarm (FP)</t>
+          <t>Cases that missed inconsistency (FP)</t>
         </is>
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>True Negatives: correctly reports consistent (TN)</t>
+          <t>Cases that correctly captures inconsistency (TN)</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>FNR = FN/(FN+TP)</t>
+          <t>FPR</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
@@ -1333,17 +1333,17 @@
         <v/>
       </c>
       <c r="H22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J22">
         <f>IF(I22&gt;0,(H22/I22)*100,0)</f>
         <v/>
       </c>
       <c r="K22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
@@ -1366,18 +1366,18 @@
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S22">
         <f>IF(Q22+R22&gt;0,Q22/(Q22+R22),0)</f>
         <v/>
       </c>
       <c r="T22">
-        <f>IF(K22+N22&gt;0,K22/(K22+N22),0)</f>
+        <f>IF(O22+L22&gt;0,O22/(O22+L22),0)</f>
         <v/>
       </c>
       <c r="U22">
-        <f>IF(K22+L22&gt;0,K22/(K22+L22),0)</f>
+        <f>IF(O22+N22&gt;0,O22/(O22+N22),0)</f>
         <v/>
       </c>
       <c r="V22">
@@ -1412,17 +1412,17 @@
         <v/>
       </c>
       <c r="H23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J23">
         <f>IF(I23&gt;0,(H23/I23)*100,0)</f>
         <v/>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
@@ -1445,18 +1445,18 @@
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S23">
         <f>IF(Q23+R23&gt;0,Q23/(Q23+R23),0)</f>
         <v/>
       </c>
       <c r="T23">
-        <f>IF(K23+N23&gt;0,K23/(K23+N23),0)</f>
+        <f>IF(O23+L23&gt;0,O23/(O23+L23),0)</f>
         <v/>
       </c>
       <c r="U23">
-        <f>IF(K23+L23&gt;0,K23/(K23+L23),0)</f>
+        <f>IF(O23+N23&gt;0,O23/(O23+N23),0)</f>
         <v/>
       </c>
       <c r="V23">
@@ -1491,17 +1491,17 @@
         <v/>
       </c>
       <c r="H24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J24">
         <f>IF(I24&gt;0,(H24/I24)*100,0)</f>
         <v/>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
@@ -1524,18 +1524,18 @@
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S24">
         <f>IF(Q24+R24&gt;0,Q24/(Q24+R24),0)</f>
         <v/>
       </c>
       <c r="T24">
-        <f>IF(K24+N24&gt;0,K24/(K24+N24),0)</f>
+        <f>IF(O24+L24&gt;0,O24/(O24+L24),0)</f>
         <v/>
       </c>
       <c r="U24">
-        <f>IF(K24+L24&gt;0,K24/(K24+L24),0)</f>
+        <f>IF(O24+N24&gt;0,O24/(O24+N24),0)</f>
         <v/>
       </c>
       <c r="V24">
@@ -1570,17 +1570,17 @@
         <v/>
       </c>
       <c r="H25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J25">
         <f>IF(I25&gt;0,(H25/I25)*100,0)</f>
         <v/>
       </c>
       <c r="K25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
@@ -1593,7 +1593,7 @@
         <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P25">
         <f>IF(N25+O25&gt;0,N25/(N25+O25),0)</f>
@@ -1603,18 +1603,18 @@
         <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S25">
         <f>IF(Q25+R25&gt;0,Q25/(Q25+R25),0)</f>
         <v/>
       </c>
       <c r="T25">
-        <f>IF(K25+N25&gt;0,K25/(K25+N25),0)</f>
+        <f>IF(O25+L25&gt;0,O25/(O25+L25),0)</f>
         <v/>
       </c>
       <c r="U25">
-        <f>IF(K25+L25&gt;0,K25/(K25+L25),0)</f>
+        <f>IF(O25+N25&gt;0,O25/(O25+N25),0)</f>
         <v/>
       </c>
       <c r="V25">
@@ -1649,17 +1649,17 @@
         <v/>
       </c>
       <c r="H26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J26">
         <f>IF(I26&gt;0,(H26/I26)*100,0)</f>
         <v/>
       </c>
       <c r="K26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
@@ -1672,7 +1672,7 @@
         <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P26">
         <f>IF(N26+O26&gt;0,N26/(N26+O26),0)</f>
@@ -1682,18 +1682,18 @@
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S26">
         <f>IF(Q26+R26&gt;0,Q26/(Q26+R26),0)</f>
         <v/>
       </c>
       <c r="T26">
-        <f>IF(K26+N26&gt;0,K26/(K26+N26),0)</f>
+        <f>IF(O26+L26&gt;0,O26/(O26+L26),0)</f>
         <v/>
       </c>
       <c r="U26">
-        <f>IF(K26+L26&gt;0,K26/(K26+L26),0)</f>
+        <f>IF(O26+N26&gt;0,O26/(O26+N26),0)</f>
         <v/>
       </c>
       <c r="V26">
@@ -1728,10 +1728,10 @@
         <v/>
       </c>
       <c r="H27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J27">
         <f>IF(I27&gt;0,(H27/I27)*100,0)</f>
@@ -1741,14 +1741,14 @@
         <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M27">
         <f>IF(K27+L27&gt;0,K27/(K27+L27),0)</f>
         <v/>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -1758,7 +1758,7 @@
         <v/>
       </c>
       <c r="Q27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
@@ -1768,11 +1768,11 @@
         <v/>
       </c>
       <c r="T27">
-        <f>IF(K27+N27&gt;0,K27/(K27+N27),0)</f>
+        <f>IF(O27+L27&gt;0,O27/(O27+L27),0)</f>
         <v/>
       </c>
       <c r="U27">
-        <f>IF(K27+L27&gt;0,K27/(K27+L27),0)</f>
+        <f>IF(O27+N27&gt;0,O27/(O27+N27),0)</f>
         <v/>
       </c>
       <c r="V27">
@@ -1807,17 +1807,17 @@
         <v/>
       </c>
       <c r="H28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J28">
         <f>IF(I28&gt;0,(H28/I28)*100,0)</f>
         <v/>
       </c>
       <c r="K28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
@@ -1830,7 +1830,7 @@
         <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P28">
         <f>IF(N28+O28&gt;0,N28/(N28+O28),0)</f>
@@ -1840,18 +1840,18 @@
         <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S28">
         <f>IF(Q28+R28&gt;0,Q28/(Q28+R28),0)</f>
         <v/>
       </c>
       <c r="T28">
-        <f>IF(K28+N28&gt;0,K28/(K28+N28),0)</f>
+        <f>IF(O28+L28&gt;0,O28/(O28+L28),0)</f>
         <v/>
       </c>
       <c r="U28">
-        <f>IF(K28+L28&gt;0,K28/(K28+L28),0)</f>
+        <f>IF(O28+N28&gt;0,O28/(O28+N28),0)</f>
         <v/>
       </c>
       <c r="V28">
@@ -1886,10 +1886,10 @@
         <v/>
       </c>
       <c r="H29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J29">
         <f>IF(I29&gt;0,(H29/I29)*100,0)</f>
@@ -1899,7 +1899,7 @@
         <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M29">
         <f>IF(K29+L29&gt;0,K29/(K29+L29),0)</f>
@@ -1909,14 +1909,14 @@
         <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P29">
         <f>IF(N29+O29&gt;0,N29/(N29+O29),0)</f>
         <v/>
       </c>
       <c r="Q29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -1926,11 +1926,11 @@
         <v/>
       </c>
       <c r="T29">
-        <f>IF(K29+N29&gt;0,K29/(K29+N29),0)</f>
+        <f>IF(O29+L29&gt;0,O29/(O29+L29),0)</f>
         <v/>
       </c>
       <c r="U29">
-        <f>IF(K29+L29&gt;0,K29/(K29+L29),0)</f>
+        <f>IF(O29+N29&gt;0,O29/(O29+N29),0)</f>
         <v/>
       </c>
       <c r="V29">
@@ -1965,17 +1965,17 @@
         <v/>
       </c>
       <c r="H30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J30">
         <f>IF(I30&gt;0,(H30/I30)*100,0)</f>
         <v/>
       </c>
       <c r="K30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
@@ -1998,18 +1998,18 @@
         <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S30">
         <f>IF(Q30+R30&gt;0,Q30/(Q30+R30),0)</f>
         <v/>
       </c>
       <c r="T30">
-        <f>IF(K30+N30&gt;0,K30/(K30+N30),0)</f>
+        <f>IF(O30+L30&gt;0,O30/(O30+L30),0)</f>
         <v/>
       </c>
       <c r="U30">
-        <f>IF(K30+L30&gt;0,K30/(K30+L30),0)</f>
+        <f>IF(O30+N30&gt;0,O30/(O30+N30),0)</f>
         <v/>
       </c>
       <c r="V30">
@@ -2044,17 +2044,17 @@
         <v/>
       </c>
       <c r="H31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J31">
         <f>IF(I31&gt;0,(H31/I31)*100,0)</f>
         <v/>
       </c>
       <c r="K31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
@@ -2077,18 +2077,18 @@
         <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S31">
         <f>IF(Q31+R31&gt;0,Q31/(Q31+R31),0)</f>
         <v/>
       </c>
       <c r="T31">
-        <f>IF(K31+N31&gt;0,K31/(K31+N31),0)</f>
+        <f>IF(O31+L31&gt;0,O31/(O31+L31),0)</f>
         <v/>
       </c>
       <c r="U31">
-        <f>IF(K31+L31&gt;0,K31/(K31+L31),0)</f>
+        <f>IF(O31+N31&gt;0,O31/(O31+N31),0)</f>
         <v/>
       </c>
       <c r="V31">
